--- a/IPAM-Lernfeld 9.xlsx
+++ b/IPAM-Lernfeld 9.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onndr-my.sharepoint.com/personal/l_riewerts_ndr_de/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF09D304-F4B0-4119-9246-5579E94C9910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="383" documentId="8_{FF09D304-F4B0-4119-9246-5579E94C9910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C8D6FFC-1DEF-41DF-A41B-58A2D3528478}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{40DFBA2E-B5A5-4B48-80F5-BCEF6C02529A}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{40DFBA2E-B5A5-4B48-80F5-BCEF6C02529A}"/>
   </bookViews>
   <sheets>
     <sheet name="Prefixe" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="172">
   <si>
     <t>ID</t>
   </si>
@@ -332,16 +332,247 @@
   </si>
   <si>
     <t>Router-B</t>
+  </si>
+  <si>
+    <t>Router HH</t>
+  </si>
+  <si>
+    <t>Router-M</t>
+  </si>
+  <si>
+    <t>Router-HL</t>
+  </si>
+  <si>
+    <t>Se0/1/1</t>
+  </si>
+  <si>
+    <t>Se0/2/0</t>
+  </si>
+  <si>
+    <t>SW-HH-01</t>
+  </si>
+  <si>
+    <t>Se0/1/2</t>
+  </si>
+  <si>
+    <t>Se0/2/1</t>
+  </si>
+  <si>
+    <t>SW-HL-01</t>
+  </si>
+  <si>
+    <t>SW-B-01</t>
+  </si>
+  <si>
+    <t>Hamburg</t>
+  </si>
+  <si>
+    <t>Lübeck</t>
+  </si>
+  <si>
+    <t>Berlin</t>
+  </si>
+  <si>
+    <t>SW-M-01</t>
+  </si>
+  <si>
+    <t>München</t>
+  </si>
+  <si>
+    <t>fd00:db8:0103::0</t>
+  </si>
+  <si>
+    <t>fd00:db8:0103::1</t>
+  </si>
+  <si>
+    <t>fd00:db8:0102::0</t>
+  </si>
+  <si>
+    <t>fd00:db8:0102::1</t>
+  </si>
+  <si>
+    <t>fd00:db8:0104::0</t>
+  </si>
+  <si>
+    <t>fd00:db8:0104::1</t>
+  </si>
+  <si>
+    <t>fd00:db8:0204::0</t>
+  </si>
+  <si>
+    <t>fd00:db8:0204::1</t>
+  </si>
+  <si>
+    <t>fd00:db8:0304::0</t>
+  </si>
+  <si>
+    <t>fd00:db8:0304::1</t>
+  </si>
+  <si>
+    <t>fd00:db8:0203::0</t>
+  </si>
+  <si>
+    <t>fd00:db8:0203::1</t>
+  </si>
+  <si>
+    <t>Gi1/0/2</t>
+  </si>
+  <si>
+    <t>Access</t>
+  </si>
+  <si>
+    <t>Gi1/0/11</t>
+  </si>
+  <si>
+    <t>nein</t>
+  </si>
+  <si>
+    <t>HH-Clients20</t>
+  </si>
+  <si>
+    <t>HH-Clients10</t>
+  </si>
+  <si>
+    <t>Gi1/0/12</t>
+  </si>
+  <si>
+    <t>Gi1/0/24</t>
+  </si>
+  <si>
+    <t>SW-HH-02</t>
+  </si>
+  <si>
+    <t>SW-HH-03</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>L3-Uplink</t>
+  </si>
+  <si>
+    <t>Gi1/0/1</t>
+  </si>
+  <si>
+    <t>C3650</t>
+  </si>
+  <si>
+    <t>Routed</t>
+  </si>
+  <si>
+    <t>ja</t>
+  </si>
+  <si>
+    <t>Vlan10</t>
+  </si>
+  <si>
+    <t>Vlan20</t>
+  </si>
+  <si>
+    <t>Vlan30</t>
+  </si>
+  <si>
+    <t>Vlan40</t>
+  </si>
+  <si>
+    <t>Router-HH Gi0/0/0</t>
+  </si>
+  <si>
+    <t>Vlan50</t>
+  </si>
+  <si>
+    <t>Vlan60</t>
+  </si>
+  <si>
+    <t>Transit ULA</t>
+  </si>
+  <si>
+    <t>SVI</t>
+  </si>
+  <si>
+    <t>B-V60</t>
+  </si>
+  <si>
+    <t>HL-Clients 10</t>
+  </si>
+  <si>
+    <t>HL-Clients 20</t>
+  </si>
+  <si>
+    <t>B-Server</t>
+  </si>
+  <si>
+    <t>Default Gateway VLAN 10</t>
+  </si>
+  <si>
+    <t>M-Server</t>
+  </si>
+  <si>
+    <t>Default Gateway VLAN 20</t>
+  </si>
+  <si>
+    <t>Default Gateway VLAN 30</t>
+  </si>
+  <si>
+    <t>Default Gateway VLAN 40</t>
+  </si>
+  <si>
+    <t>Default Gateway VLAN 50</t>
+  </si>
+  <si>
+    <t>Default Gateway VLAN 60</t>
+  </si>
+  <si>
+    <t>Access-Port</t>
+  </si>
+  <si>
+    <t>Gi0/0/0</t>
+  </si>
+  <si>
+    <t>fd00:db8:0200:ff00::0</t>
+  </si>
+  <si>
+    <t>fd00:db8:0300:ff00::0</t>
+  </si>
+  <si>
+    <t>fd00:db8:0400:ff00::0</t>
+  </si>
+  <si>
+    <t>fd00:db8:0100:ff00::0</t>
+  </si>
+  <si>
+    <t>fd00:db8:0400:ff00::1</t>
+  </si>
+  <si>
+    <t>fd00:db8:0100:ff00::1</t>
+  </si>
+  <si>
+    <t>fd00:db8:0200:ff00::1</t>
+  </si>
+  <si>
+    <t>fd00:db8:0300:ff00::1</t>
+  </si>
+  <si>
+    <t>Access.Port</t>
+  </si>
+  <si>
+    <t>aktiv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -384,6 +615,69 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{57D3E9A3-29AB-40B2-BACD-2DD884BA7E63}" name="Tabelle3" displayName="Tabelle3" ref="A1:J17" totalsRowShown="0">
+  <autoFilter ref="A1:J17" xr:uid="{57D3E9A3-29AB-40B2-BACD-2DD884BA7E63}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{DDD05363-5BD5-4E21-B99C-1724D76C75A9}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{AC47E9E9-A6BE-4112-8B08-565B51364D08}" name="Standort"/>
+    <tableColumn id="3" xr3:uid="{FE5F8810-C0A9-4169-A968-192E3F2083D3}" name="Netztyp"/>
+    <tableColumn id="4" xr3:uid="{41BC8DA2-F4B3-4216-8A23-1C74BDB57FC5}" name="Prefix-Typ"/>
+    <tableColumn id="5" xr3:uid="{BA6EAE40-83A8-4B58-BC05-05439D00598E}" name="VLAN-ID"/>
+    <tableColumn id="6" xr3:uid="{DE0247DC-4E4E-46A4-AE84-1307630E106D}" name="Prefix"/>
+    <tableColumn id="7" xr3:uid="{088C32D5-B874-4B4B-BCA8-E9DEE750FD4C}" name="Prefix-Länge"/>
+    <tableColumn id="8" xr3:uid="{00FE5CCF-AE9E-46DA-A364-578D99034E65}" name="Gateway"/>
+    <tableColumn id="9" xr3:uid="{99356B8F-CD61-4B06-9EDA-4698A3A9DC12}" name="Zweck"/>
+    <tableColumn id="10" xr3:uid="{E25D63BF-2680-4D16-86E5-30646904B2C5}" name="Bemerkung"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9408BF11-05F2-496A-A546-EFBB45C01E8A}" name="Tabelle1" displayName="Tabelle1" ref="A1:L27" totalsRowShown="0">
+  <autoFilter ref="A1:L27" xr:uid="{9408BF11-05F2-496A-A546-EFBB45C01E8A}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{AC0F85E1-1480-4D04-A3B7-1C98E292B643}" name="Gerät"/>
+    <tableColumn id="2" xr3:uid="{CE7F4965-491C-40CD-A967-1D471E7B71D5}" name="Gerätetyp"/>
+    <tableColumn id="3" xr3:uid="{EB9DA938-462A-43FD-99B3-CD53DE4ED6B8}" name="Standort"/>
+    <tableColumn id="4" xr3:uid="{274E42ED-3D68-49C4-A4BF-EDF77C24581B}" name="Interface"/>
+    <tableColumn id="5" xr3:uid="{0D3B92DC-FB28-47DC-B6D6-C9B4C2929229}" name="Rollen-Typ"/>
+    <tableColumn id="6" xr3:uid="{EFD51500-5EF1-4405-80A2-61334BDC6DA1}" name="Zugehöriges Netz"/>
+    <tableColumn id="7" xr3:uid="{83C147B9-4C1A-44E3-8E6D-78547B2EB5B1}" name="IPv6 Adresse"/>
+    <tableColumn id="8" xr3:uid="{1AAA6061-ACFF-427E-8141-18FF2BF2CC95}" name="Prefix-Länge"/>
+    <tableColumn id="9" xr3:uid="{9D496640-BA8C-408E-819B-B0A2AF983997}" name="Gegenstelle-Gerät"/>
+    <tableColumn id="10" xr3:uid="{3CC7FC17-FE88-4B40-A392-6547EF448494}" name="Gegenstelle-Interface"/>
+    <tableColumn id="11" xr3:uid="{C1D5BAAC-40B0-4077-B0D5-1F3AAA83FD94}" name="Status"/>
+    <tableColumn id="12" xr3:uid="{9A65768C-49F9-4F88-A231-9E786C60D8A2}" name="Bemerkung"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AEA28181-3D10-4338-A708-F9E4663865E9}" name="Tabelle4" displayName="Tabelle4" ref="A1:J8" totalsRowShown="0">
+  <autoFilter ref="A1:J8" xr:uid="{AEA28181-3D10-4338-A708-F9E4663865E9}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{4A174D55-EFBF-4AF5-801F-5EA68DDFFF7B}" name="Switch"/>
+    <tableColumn id="2" xr3:uid="{470F8E3C-5F0E-4112-A3F5-C05278B2B91C}" name="Standort"/>
+    <tableColumn id="3" xr3:uid="{20854150-C63A-4616-B625-8D4C45C4B80B}" name="VLAN-ID"/>
+    <tableColumn id="4" xr3:uid="{3505AC2C-6D47-4548-8DB9-0C479A9DAC4D}" name="VLAN-Name"/>
+    <tableColumn id="5" xr3:uid="{E9446CA7-30F6-44EF-8995-BD2C37D55238}" name="Port von"/>
+    <tableColumn id="6" xr3:uid="{634610F2-46D0-46DC-A0D5-1775766A6335}" name="Port bis"/>
+    <tableColumn id="7" xr3:uid="{51D0F6E3-3041-4A5D-955C-F407285496EB}" name="Portmodus"/>
+    <tableColumn id="8" xr3:uid="{49D75CD4-0F86-48F8-8CFF-6EDDE6A70149}" name="Uplink ja/nein"/>
+    <tableColumn id="9" xr3:uid="{52A80C15-A2E6-4D91-B819-BEFEFF03C248}" name="Uplink-Ziel"/>
+    <tableColumn id="10" xr3:uid="{B3B40B73-C080-41F8-9305-E8B6BF5A8306}" name="Bemerkung"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -707,9 +1001,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="31.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
     <col min="8" max="8" width="22.140625" customWidth="1"/>
     <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1150,17 +1447,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E623F6C0-2550-47E7-A1C2-88F2ACB47CD5}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" customWidth="1"/>
     <col min="10" max="10" width="21.140625" customWidth="1"/>
+    <col min="12" max="12" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1220,6 +1524,9 @@
       <c r="F2" t="s">
         <v>71</v>
       </c>
+      <c r="G2" t="s">
+        <v>112</v>
+      </c>
       <c r="H2">
         <v>127</v>
       </c>
@@ -1229,16 +1536,887 @@
       <c r="J2" t="s">
         <v>94</v>
       </c>
+      <c r="K2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H3">
+        <v>127</v>
+      </c>
+      <c r="I3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4">
+        <v>127</v>
+      </c>
+      <c r="I4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5">
+        <v>127</v>
+      </c>
+      <c r="I5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H6">
+        <v>127</v>
+      </c>
+      <c r="I6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H7">
+        <v>127</v>
+      </c>
+      <c r="I7" t="s">
+        <v>92</v>
+      </c>
+      <c r="J7" t="s">
+        <v>104</v>
+      </c>
+      <c r="K7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H8">
+        <v>127</v>
+      </c>
+      <c r="I8" t="s">
+        <v>99</v>
+      </c>
+      <c r="J8" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9">
+        <v>127</v>
+      </c>
+      <c r="I9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J9" t="s">
+        <v>100</v>
+      </c>
+      <c r="K9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10">
+        <v>127</v>
+      </c>
+      <c r="I10" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11">
+        <v>127</v>
+      </c>
+      <c r="I11" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11" t="s">
+        <v>103</v>
+      </c>
+      <c r="K11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12">
+        <v>127</v>
+      </c>
+      <c r="I12" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" t="s">
+        <v>101</v>
+      </c>
+      <c r="K12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" t="s">
+        <v>123</v>
+      </c>
+      <c r="H13">
+        <v>127</v>
+      </c>
+      <c r="I13" t="s">
+        <v>99</v>
+      </c>
+      <c r="J13" t="s">
+        <v>104</v>
+      </c>
+      <c r="K13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E14" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14">
+        <v>64</v>
+      </c>
+      <c r="K14" t="s">
+        <v>171</v>
+      </c>
+      <c r="L14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15">
+        <v>64</v>
+      </c>
+      <c r="K15" t="s">
+        <v>171</v>
+      </c>
+      <c r="L15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" t="s">
+        <v>148</v>
+      </c>
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16">
+        <v>64</v>
+      </c>
+      <c r="K16" t="s">
+        <v>171</v>
+      </c>
+      <c r="L16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E17" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17">
+        <v>64</v>
+      </c>
+      <c r="K17" t="s">
+        <v>171</v>
+      </c>
+      <c r="L17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18">
+        <v>64</v>
+      </c>
+      <c r="K18" t="s">
+        <v>171</v>
+      </c>
+      <c r="L18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19">
+        <v>64</v>
+      </c>
+      <c r="K19" t="s">
+        <v>171</v>
+      </c>
+      <c r="L19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E20" t="s">
+        <v>160</v>
+      </c>
+      <c r="F20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" t="s">
+        <v>165</v>
+      </c>
+      <c r="H20">
+        <v>127</v>
+      </c>
+      <c r="I20" t="s">
+        <v>102</v>
+      </c>
+      <c r="J20" t="s">
+        <v>136</v>
+      </c>
+      <c r="K20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" t="s">
+        <v>160</v>
+      </c>
+      <c r="F21" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" t="s">
+        <v>167</v>
+      </c>
+      <c r="H21">
+        <v>127</v>
+      </c>
+      <c r="I21" t="s">
+        <v>92</v>
+      </c>
+      <c r="J21" t="s">
+        <v>161</v>
+      </c>
+      <c r="K21" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" t="s">
+        <v>160</v>
+      </c>
+      <c r="F22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" t="s">
+        <v>162</v>
+      </c>
+      <c r="H22">
+        <v>127</v>
+      </c>
+      <c r="I22" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" t="s">
+        <v>136</v>
+      </c>
+      <c r="K22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" t="s">
+        <v>170</v>
+      </c>
+      <c r="F23" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" t="s">
+        <v>168</v>
+      </c>
+      <c r="H23">
+        <v>127</v>
+      </c>
+      <c r="I23" t="s">
+        <v>99</v>
+      </c>
+      <c r="J23" t="s">
+        <v>161</v>
+      </c>
+      <c r="K23" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" t="s">
+        <v>163</v>
+      </c>
+      <c r="H24">
+        <v>127</v>
+      </c>
+      <c r="I24" t="s">
+        <v>106</v>
+      </c>
+      <c r="J24" t="s">
+        <v>136</v>
+      </c>
+      <c r="K24" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" t="s">
+        <v>160</v>
+      </c>
+      <c r="F25" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" t="s">
+        <v>169</v>
+      </c>
+      <c r="H25">
+        <v>127</v>
+      </c>
+      <c r="I25" t="s">
+        <v>96</v>
+      </c>
+      <c r="J25" t="s">
+        <v>161</v>
+      </c>
+      <c r="K25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" t="s">
+        <v>161</v>
+      </c>
+      <c r="E26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F26" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" t="s">
+        <v>164</v>
+      </c>
+      <c r="H26">
+        <v>127</v>
+      </c>
+      <c r="I26" t="s">
+        <v>110</v>
+      </c>
+      <c r="J26" t="s">
+        <v>136</v>
+      </c>
+      <c r="K26" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" t="s">
+        <v>166</v>
+      </c>
+      <c r="H27">
+        <v>127</v>
+      </c>
+      <c r="I27" t="s">
+        <v>98</v>
+      </c>
+      <c r="J27" t="s">
+        <v>161</v>
+      </c>
+      <c r="K27" t="s">
+        <v>171</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2082E327-1B63-45D9-BD64-375B0703DC2A}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1272,7 +2450,198 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I4" t="s">
+        <v>144</v>
+      </c>
+      <c r="J4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8">
+        <v>60</v>
+      </c>
+      <c r="D8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/IPAM-Lernfeld 9.xlsx
+++ b/IPAM-Lernfeld 9.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onndr-my.sharepoint.com/personal/l_riewerts_ndr_de/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="383" documentId="8_{FF09D304-F4B0-4119-9246-5579E94C9910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C8D6FFC-1DEF-41DF-A41B-58A2D3528478}"/>
+  <xr:revisionPtr revIDLastSave="395" documentId="8_{FF09D304-F4B0-4119-9246-5579E94C9910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A8822D8-0059-4463-BD09-C4665C54FBD0}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{40DFBA2E-B5A5-4B48-80F5-BCEF6C02529A}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{40DFBA2E-B5A5-4B48-80F5-BCEF6C02529A}"/>
   </bookViews>
   <sheets>
     <sheet name="Prefixe" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="170">
   <si>
     <t>ID</t>
   </si>
@@ -350,12 +350,6 @@
   </si>
   <si>
     <t>SW-HH-01</t>
-  </si>
-  <si>
-    <t>Se0/1/2</t>
-  </si>
-  <si>
-    <t>Se0/2/1</t>
   </si>
   <si>
     <t>SW-HL-01</t>
@@ -1525,7 +1519,7 @@
         <v>71</v>
       </c>
       <c r="G2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H2">
         <v>127</v>
@@ -1537,7 +1531,7 @@
         <v>94</v>
       </c>
       <c r="K2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1551,7 +1545,7 @@
         <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>95</v>
@@ -1560,7 +1554,7 @@
         <v>71</v>
       </c>
       <c r="G3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H3">
         <v>127</v>
@@ -1569,10 +1563,10 @@
         <v>92</v>
       </c>
       <c r="J3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1595,7 +1589,7 @@
         <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H4">
         <v>127</v>
@@ -1607,7 +1601,7 @@
         <v>100</v>
       </c>
       <c r="K4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1621,7 +1615,7 @@
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>95</v>
@@ -1630,7 +1624,7 @@
         <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H5">
         <v>127</v>
@@ -1639,10 +1633,10 @@
         <v>92</v>
       </c>
       <c r="J5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1665,7 +1659,7 @@
         <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H6">
         <v>127</v>
@@ -1677,7 +1671,7 @@
         <v>101</v>
       </c>
       <c r="K6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1691,7 +1685,7 @@
         <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
         <v>95</v>
@@ -1700,7 +1694,7 @@
         <v>67</v>
       </c>
       <c r="G7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H7">
         <v>127</v>
@@ -1709,10 +1703,10 @@
         <v>92</v>
       </c>
       <c r="J7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1735,7 +1729,7 @@
         <v>68</v>
       </c>
       <c r="G8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H8">
         <v>127</v>
@@ -1747,7 +1741,7 @@
         <v>94</v>
       </c>
       <c r="K8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1761,7 +1755,7 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>95</v>
@@ -1770,7 +1764,7 @@
         <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H9">
         <v>127</v>
@@ -1779,10 +1773,10 @@
         <v>98</v>
       </c>
       <c r="J9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1805,7 +1799,7 @@
         <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H10">
         <v>127</v>
@@ -1817,7 +1811,7 @@
         <v>100</v>
       </c>
       <c r="K10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1831,7 +1825,7 @@
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>95</v>
@@ -1840,7 +1834,7 @@
         <v>69</v>
       </c>
       <c r="G11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H11">
         <v>127</v>
@@ -1849,10 +1843,10 @@
         <v>98</v>
       </c>
       <c r="J11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1875,7 +1869,7 @@
         <v>70</v>
       </c>
       <c r="G12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H12">
         <v>127</v>
@@ -1887,7 +1881,7 @@
         <v>101</v>
       </c>
       <c r="K12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1901,7 +1895,7 @@
         <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>95</v>
@@ -1910,7 +1904,7 @@
         <v>70</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H13">
         <v>127</v>
@@ -1919,10 +1913,10 @@
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K13" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1930,16 +1924,16 @@
         <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
@@ -1951,10 +1945,10 @@
         <v>64</v>
       </c>
       <c r="K14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1962,16 +1956,16 @@
         <v>102</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F15" t="s">
         <v>33</v>
@@ -1983,27 +1977,27 @@
         <v>64</v>
       </c>
       <c r="K15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
         <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F16" t="s">
         <v>37</v>
@@ -2015,27 +2009,27 @@
         <v>64</v>
       </c>
       <c r="K16" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s">
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F17" t="s">
         <v>38</v>
@@ -2047,27 +2041,27 @@
         <v>64</v>
       </c>
       <c r="K17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C18" t="s">
         <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E18" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F18" t="s">
         <v>39</v>
@@ -2079,30 +2073,30 @@
         <v>64</v>
       </c>
       <c r="K18" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
         <v>43</v>
       </c>
       <c r="D19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E19" t="s">
         <v>146</v>
       </c>
-      <c r="E19" t="s">
-        <v>148</v>
-      </c>
       <c r="F19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G19" t="s">
         <v>51</v>
@@ -2111,10 +2105,10 @@
         <v>64</v>
       </c>
       <c r="K19" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -2128,16 +2122,16 @@
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F20" t="s">
         <v>83</v>
       </c>
       <c r="G20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H20">
         <v>127</v>
@@ -2146,10 +2140,10 @@
         <v>102</v>
       </c>
       <c r="J20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -2157,22 +2151,22 @@
         <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F21" t="s">
         <v>83</v>
       </c>
       <c r="G21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H21">
         <v>127</v>
@@ -2181,10 +2175,10 @@
         <v>92</v>
       </c>
       <c r="J21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -2198,51 +2192,51 @@
         <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F22" t="s">
         <v>82</v>
       </c>
       <c r="G22" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H22">
         <v>127</v>
       </c>
       <c r="I22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K22" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C23" t="s">
         <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F23" t="s">
         <v>82</v>
       </c>
       <c r="G23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H23">
         <v>127</v>
@@ -2251,10 +2245,10 @@
         <v>99</v>
       </c>
       <c r="J23" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -2268,51 +2262,51 @@
         <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F24" t="s">
         <v>84</v>
       </c>
       <c r="G24" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H24">
         <v>127</v>
       </c>
       <c r="I24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C25" t="s">
         <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E25" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F25" t="s">
         <v>84</v>
       </c>
       <c r="G25" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H25">
         <v>127</v>
@@ -2321,10 +2315,10 @@
         <v>96</v>
       </c>
       <c r="J25" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2338,51 +2332,51 @@
         <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F26" t="s">
         <v>85</v>
       </c>
       <c r="G26" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H26">
         <v>127</v>
       </c>
       <c r="I26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C27" t="s">
         <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F27" t="s">
         <v>85</v>
       </c>
       <c r="G27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H27">
         <v>127</v>
@@ -2391,10 +2385,10 @@
         <v>98</v>
       </c>
       <c r="J27" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K27" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2455,187 +2449,187 @@
         <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" t="s">
         <v>124</v>
       </c>
-      <c r="F2" t="s">
-        <v>126</v>
-      </c>
       <c r="G2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" t="s">
         <v>125</v>
-      </c>
-      <c r="H2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
       <c r="D3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" t="s">
         <v>128</v>
       </c>
-      <c r="E3" t="s">
-        <v>130</v>
-      </c>
       <c r="F3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" t="s">
         <v>125</v>
-      </c>
-      <c r="H3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" t="s">
         <v>133</v>
       </c>
-      <c r="B4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>134</v>
       </c>
-      <c r="D4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" t="s">
         <v>136</v>
       </c>
-      <c r="F4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G4" t="s">
-        <v>138</v>
-      </c>
       <c r="H4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5">
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" t="s">
         <v>124</v>
       </c>
-      <c r="F5" t="s">
-        <v>126</v>
-      </c>
       <c r="G5" t="s">
+        <v>123</v>
+      </c>
+      <c r="H5" t="s">
         <v>125</v>
-      </c>
-      <c r="H5" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6">
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" t="s">
         <v>125</v>
-      </c>
-      <c r="H6" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C7">
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" t="s">
         <v>124</v>
       </c>
-      <c r="F7" t="s">
-        <v>126</v>
-      </c>
       <c r="G7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" t="s">
         <v>125</v>
-      </c>
-      <c r="H7" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C8">
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" t="s">
         <v>124</v>
       </c>
-      <c r="F8" t="s">
-        <v>126</v>
-      </c>
       <c r="G8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" t="s">
         <v>125</v>
-      </c>
-      <c r="H8" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
